--- a/examples/jack+jill.xlsx
+++ b/examples/jack+jill.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Dropbox\Retirement\MyProject\Owl\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A295070-C45F-446F-97F6-D3E258D0BA4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64A8F46-BCD3-4A85-BE4A-4B5800FAC2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10690" yWindow="7090" windowWidth="19420" windowHeight="11500" xr2:uid="{10BCA99F-290D-43B0-90F7-A2A56377E151}"/>
+    <workbookView xWindow="345" yWindow="8055" windowWidth="15045" windowHeight="11700" xr2:uid="{10BCA99F-290D-43B0-90F7-A2A56377E151}"/>
   </bookViews>
   <sheets>
     <sheet name="Jack" sheetId="1" r:id="rId1"/>
@@ -70,10 +70,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,6 +84,12 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -109,10 +116,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="5" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -428,7 +439,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB57614-FCF1-4139-AA0D-31AF55A08D66}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
@@ -476,90 +487,93 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2025</v>
-      </c>
-      <c r="B2" s="1">
-        <v>100000</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1">
-        <v>15000</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="A2" s="3">
+        <v>2020</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4">
+        <v>6500</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2026</v>
-      </c>
-      <c r="B3" s="1">
-        <v>100000</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1">
-        <v>15000</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="I3" s="1"/>
+      <c r="A3" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4">
+        <v>6500</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2027</v>
-      </c>
-      <c r="B4" s="1">
-        <v>100000</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1">
-        <v>50000</v>
-      </c>
-      <c r="I4" s="1"/>
+      <c r="A4" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4">
+        <v>7000</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2028</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1">
-        <v>50000</v>
-      </c>
-      <c r="I5" s="1"/>
+      <c r="A5" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4">
+        <v>7000</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2029</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+      <c r="A6" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4">
+        <v>7000</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4">
+        <v>20000</v>
+      </c>
+      <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2030</v>
-      </c>
-      <c r="B7" s="1"/>
+        <v>2025</v>
+      </c>
+      <c r="B7" s="1">
+        <v>100000</v>
+      </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" s="1">
+        <v>15000</v>
+      </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -568,11 +582,15 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>2031</v>
-      </c>
-      <c r="B8" s="1"/>
+        <v>2026</v>
+      </c>
+      <c r="B8" s="1">
+        <v>100000</v>
+      </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+      <c r="D8" s="1">
+        <v>15000</v>
+      </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -581,20 +599,24 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2032</v>
-      </c>
-      <c r="B9" s="1"/>
+        <v>2027</v>
+      </c>
+      <c r="B9" s="1">
+        <v>100000</v>
+      </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="H9" s="1">
+        <v>50000</v>
+      </c>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>2033</v>
+        <v>2028</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -602,12 +624,14 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
+      <c r="H10" s="1">
+        <v>50000</v>
+      </c>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>2034</v>
+        <v>2029</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -620,7 +644,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -633,7 +657,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>2036</v>
+        <v>2031</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -646,7 +670,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>2037</v>
+        <v>2032</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -659,7 +683,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>2038</v>
+        <v>2033</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -672,7 +696,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>2039</v>
+        <v>2034</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -685,7 +709,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>2040</v>
+        <v>2035</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -698,7 +722,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>2041</v>
+        <v>2036</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -711,7 +735,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>2042</v>
+        <v>2037</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -724,7 +748,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>2043</v>
+        <v>2038</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -737,7 +761,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>2044</v>
+        <v>2039</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -750,7 +774,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -763,7 +787,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>2046</v>
+        <v>2041</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -776,7 +800,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>2047</v>
+        <v>2042</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -789,7 +813,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>2048</v>
+        <v>2043</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -802,7 +826,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>2049</v>
+        <v>2044</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -815,7 +839,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -828,7 +852,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>2051</v>
+        <v>2046</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -841,7 +865,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>2052</v>
+        <v>2047</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -854,7 +878,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>2053</v>
+        <v>2048</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -867,7 +891,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>2054</v>
+        <v>2049</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -880,6 +904,71 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
+        <v>2050</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>2051</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>2052</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>2053</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2054</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37">
         <v>2055</v>
       </c>
     </row>
@@ -891,7 +980,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71DE7EE4-731B-47FB-9A4E-667972814602}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" customWidth="1"/>
@@ -935,222 +1024,234 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2025</v>
-      </c>
-      <c r="B2" s="1">
-        <v>80000</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="A2" s="3">
+        <v>2020</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5">
+        <v>4000</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2026</v>
-      </c>
-      <c r="B3" s="1">
-        <v>80000</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+      <c r="A3" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5">
+        <v>4000</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2027</v>
-      </c>
-      <c r="B4" s="1">
-        <v>85000</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+      <c r="A4" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5">
+        <v>4000</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2028</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+      <c r="A5" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5">
+        <v>12000</v>
+      </c>
+      <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2029</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+      <c r="A6" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5">
+        <v>5000</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2030</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+        <v>2025</v>
+      </c>
+      <c r="B7" s="6">
+        <v>80000</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>2031</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+        <v>2025</v>
+      </c>
+      <c r="B8" s="6">
+        <v>80000</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2032</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+        <v>2026</v>
+      </c>
+      <c r="B9" s="6">
+        <v>80000</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>2033</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+        <v>2027</v>
+      </c>
+      <c r="B10" s="6">
+        <v>85000</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>2034</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+        <v>2028</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>2035</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+        <v>2029</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>2036</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+        <v>2030</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>2037</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+        <v>2031</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>2038</v>
-      </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+        <v>2032</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>2039</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
+        <v>2033</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>2040</v>
-      </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+        <v>2034</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>2041</v>
+        <v>2035</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1163,7 +1264,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>2042</v>
+        <v>2036</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1176,7 +1277,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>2043</v>
+        <v>2037</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1189,7 +1290,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>2044</v>
+        <v>2038</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1202,7 +1303,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>2045</v>
+        <v>2039</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1215,7 +1316,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>2046</v>
+        <v>2040</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1228,7 +1329,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>2047</v>
+        <v>2041</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1241,7 +1342,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>2048</v>
+        <v>2042</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1254,7 +1355,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>2049</v>
+        <v>2043</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1267,7 +1368,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>2050</v>
+        <v>2044</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1280,7 +1381,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>2051</v>
+        <v>2045</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1293,7 +1394,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>2052</v>
+        <v>2046</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1306,7 +1407,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>2053</v>
+        <v>2047</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1319,7 +1420,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>2054</v>
+        <v>2048</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1332,7 +1433,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>2055</v>
+        <v>2049</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1345,7 +1446,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>2056</v>
+        <v>2050</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1358,11 +1459,89 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>2057</v>
-      </c>
+        <v>2051</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
+        <v>2052</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2053</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>2054</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2055</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>2056</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41">
         <v>2058</v>
       </c>
     </row>
